--- a/data/merged/2026-08-31/MERGED_ES_Wet-Dry-Floor-Washer_2026-08-31.xlsx
+++ b/data/merged/2026-08-31/MERGED_ES_Wet-Dry-Floor-Washer_2026-08-31.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR7"/>
+  <dimension ref="A1:BR6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -2434,56 +2434,56 @@
       <c r="B5" s="13"/>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>B0D2KT41N3</t>
+          <t>B0DGV9F4X3</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Tamaño: 16 L</t>
+          <t>Nombre de estilo: X-CLEAN 4 Negro</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Marca: Cecotec | Función especial: Húmedo/seco | Tipo de filtro: Sistema de filtración doble | Recomendación de superficie: Todos los suelos | Fuente de alimentación: Eléctrico con cable | Voltaje: 1200 Voltios | Componentes incluidos: 1 x Aspiradora; 1 x Accesorio para esquinas; 1 x Accesorio 2 en 1; 1 x Base de aspiración universal; 1 x Cargador; 1 x Cepillo para el suelo; 1 x Manual de instrucciones; 1 x Tubo extensible; 1 x Tubo flexible | ¿Es inalámbrico?: No | Peso del producto: 4,5 Kilogramos | Capacidad: 16 litros</t>
+          <t>Marca: Rowenta | Función especial: Inalámbrico | Tipo de filtro: Filtro de espuma, Filtro HEPA | Recomendación de superficie: Parquet, Mármol, Laminado, Azulejos | Fuente de alimentación: Batería | Voltaje: 18,5 Voltios | Componentes incluidos: Rodillo suave, rodillo recurrente, filtro tipo HEPA adicional, filtro de espuma adicional, cepillo de limpieza con función colador y función cortador | ¿Es inalámbrico?: Sí | Peso del producto: 5,4 Kilogramos | Capacidad: 1,1 litros</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>Rowenta</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/Cecotec/page/8A5D1609-A164-427A-9580-48312AC42537?lp_asin=B0D2KT41N3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Aspiradora con Cable en Seco y Húmedos - Aspirador Sólidos y Líquidos 16L Conga Rockstar Wet &amp; Dry Compact Garden Plus. 1200W, Ligero, Compacto, Doble Función de Succión y Soplado, Accesorios</t>
+          <t>Rowenta X-Clean 4, Aspiradora Fregona Eléctrica Sin Cable, Negro</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
-          <t>Aspirador de sólidos y líquidos de gran potencia con tanque de plástico para aspirar todo tipo de suciedad, incluidos líquidos, de cualquier rincón de tu hogar.
-Aspira sin esfuerzo gracias a su potencia de 1200 W y a su reducido peso y tamaño.
-Sistema de doble filtrado que filtra el agua y purifica el aire reteniendo de forma eficaz un gran porcentaje de alérgenos. Incluye función sopladora Blowing System.
-Gran radio de acción con más de 5 metros y porta accesorios para poder limpiar de la forma más cómoda hasta el último rincón.
-Incluye 4 accesorios para limpiar cualquier superficie de forma eficaz.</t>
+          <t>LIMPIEZA 2 EN 1: fregona eléctricainalámbrica para limpieza seca y húmeda que permite ganar tiempo aspirando y fregando enuna sola pasada, para unos resultados óptimos en todo tipo de suelos duros (madera, mármol, laminados y baldosas)
+DETECCIÓN INTELIGENTE DE LA SUCIEDAD: detección automática de la suciedad con indicadores de color en una pantalla led (rojo para la suciedad y azul cuando detecta un suelo limpio) y un ajuste automático de la velocidad de rotación del rodillo y del flujo de agua para conseguir unos óptimosresultados
+GRAN AUTONOMÍA: limpieza sin cables que marca la diferencia, con hasta 50min de autonomía para cubrir hasta 350m²dependiendo del mobiliario de la casa
+LIMPIEZA SIN ESFUERZO:diseño moderno, ligero, tan solo 1,1kg en tu mano, inteligente,con un sistema de rodillos ayudados por las ruedas, siendo necesario utilizar solo un 25 %del esfuerzo habitual
+SISTEMA DE AUTOLIMPIEZA:activa la función con tan solo pulsar un botón y, una vez lavado el rodillo, solo tienes que dejarlopreviamente secarpara que esté listo para la siguiente sesión de limpieza mientras se carga en la base</t>
         </is>
       </c>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0D2KT41N3?psc=1</t>
+          <t>https://www.amazon.es/dp/B0DGV9F4X3?psc=1</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41k5oav-AKL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31mSTnwM6cL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>B0D33D9J3P</t>
+          <t>B0DKMVFHRN</t>
         </is>
       </c>
       <c r="M5" s="14" t="inlineStr">
@@ -2497,13 +2497,11 @@
         </is>
       </c>
       <c r="O5" s="15">
-        <v>1462</v>
-      </c>
-      <c r="P5" s="15">
-        <v>-837</v>
-      </c>
+        <v>223853</v>
+      </c>
+      <c r="P5" s="15"/>
       <c r="Q5" s="16">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
       <c r="R5" s="17" t="inlineStr">
         <is>
@@ -2512,79 +2510,57 @@
       </c>
       <c r="S5" s="18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T5" s="15">
-        <v>225</v>
-      </c>
-      <c r="U5" s="16">
-        <v>-0.13</v>
-      </c>
-      <c r="V5" s="15">
-        <v>7421</v>
-      </c>
-      <c r="W5" s="15" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="X5" s="15">
-        <v>6596</v>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T5" s="15"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
       <c r="Y5" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z5" s="20">
-        <v>32.98</v>
+        <v>371.88</v>
       </c>
       <c r="AA5" s="4"/>
       <c r="AB5" s="1"/>
       <c r="AC5" s="2"/>
       <c r="AD5" s="19">
-        <v>912</v>
+        <v>783</v>
       </c>
       <c r="AE5" s="15">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AF5" s="21">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AG5" s="22">
         <v>0</v>
       </c>
-      <c r="AH5" s="20">
-        <v>10.1</v>
-      </c>
+      <c r="AH5" s="20"/>
       <c r="AI5" s="16">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AJ5"/>
       <c r="AK5" s="13" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="AL5" s="19">
-        <v>857</v>
+        <v>663</v>
       </c>
       <c r="AM5" s="13" t="inlineStr">
         <is>
           <t>AMZ</t>
         </is>
       </c>
-      <c r="AN5" s="13" t="inlineStr">
-        <is>
-          <t>8-16天</t>
-        </is>
-      </c>
+      <c r="AN5" s="13"/>
       <c r="AO5" s="13"/>
-      <c r="AP5" s="20">
-        <v>69.35</v>
-      </c>
-      <c r="AQ5" s="19">
-        <v>9</v>
-      </c>
+      <c r="AP5" s="20"/>
+      <c r="AQ5" s="19"/>
       <c r="AR5" s="19">
         <v>1</v>
       </c>
@@ -2601,11 +2577,7 @@
       <c r="AU5" s="13"/>
       <c r="AV5" s="14"/>
       <c r="AW5" s="13"/>
-      <c r="AX5" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AX5" s="13"/>
       <c r="AY5" s="13"/>
       <c r="AZ5" s="13"/>
       <c r="BA5" s="13"/>
@@ -2631,45 +2603,25 @@
       <c r="BI5"/>
       <c r="BJ5" s="23" t="inlineStr">
         <is>
-          <t>4,5 Kilogramos</t>
+          <t>5,4 Kilogramos</t>
         </is>
       </c>
       <c r="BK5" s="23" t="inlineStr">
         <is>
-          <t>4.50 kg</t>
+          <t>5.40 kg</t>
         </is>
       </c>
       <c r="BL5" s="23" t="inlineStr">
         <is>
-          <t>38l. x 33an. x 45al. centímetros</t>
+          <t>31,5l. x 30,5an. x 114,7al. centímetros</t>
         </is>
       </c>
       <c r="BM5" s="23"/>
-      <c r="BN5" s="23" t="inlineStr">
-        <is>
-          <t>5.37 kg</t>
-        </is>
-      </c>
-      <c r="BO5" s="23" t="inlineStr">
-        <is>
-          <t>5.37 kg</t>
-        </is>
-      </c>
-      <c r="BP5" s="23" t="inlineStr">
-        <is>
-          <t>40 x 36 x 36 cm</t>
-        </is>
-      </c>
-      <c r="BQ5" s="23" t="inlineStr">
-        <is>
-          <t>40.00 x 36.00 x 36.00 cm</t>
-        </is>
-      </c>
-      <c r="BR5" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
+      <c r="BN5" s="23"/>
+      <c r="BO5" s="23"/>
+      <c r="BP5" s="23"/>
+      <c r="BQ5" s="23"/>
+      <c r="BR5" s="13"/>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
@@ -2678,56 +2630,48 @@
       <c r="B6" s="13"/>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>B0DGV9F4X3</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>Nombre de estilo: X-CLEAN 4 Negro</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Marca: Rowenta | Función especial: Inalámbrico | Tipo de filtro: Filtro de espuma, Filtro HEPA | Recomendación de superficie: Parquet, Mármol, Laminado, Azulejos | Fuente de alimentación: Batería | Voltaje: 18,5 Voltios | Componentes incluidos: Rodillo suave, rodillo recurrente, filtro tipo HEPA adicional, filtro de espuma adicional, cepillo de limpieza con función colador y función cortador | ¿Es inalámbrico?: Sí | Peso del producto: 5,4 Kilogramos | Capacidad: 1,1 litros</t>
-        </is>
-      </c>
+          <t>B0H8ZM49W9</t>
+        </is>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Rowenta</t>
+          <t>KSIWEHDSS</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=KSIWEHDSS</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>Rowenta X-Clean 4, Aspiradora Fregona Eléctrica Sin Cable, Negro</t>
+          <t>Aspiradoras de Mano, Aspirador Coche Potente 20000Pa,Recargable Aspiradora De Mano Sin Cable,Mini Aspiradora para Hogar,Pelo de Mascotas</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>LIMPIEZA 2 EN 1: fregona eléctricainalámbrica para limpieza seca y húmeda que permite ganar tiempo aspirando y fregando enuna sola pasada, para unos resultados óptimos en todo tipo de suelos duros (madera, mármol, laminados y baldosas)
-DETECCIÓN INTELIGENTE DE LA SUCIEDAD: detección automática de la suciedad con indicadores de color en una pantalla led (rojo para la suciedad y azul cuando detecta un suelo limpio) y un ajuste automático de la velocidad de rotación del rodillo y del flujo de agua para conseguir unos óptimosresultados
-GRAN AUTONOMÍA: limpieza sin cables que marca la diferencia, con hasta 50min de autonomía para cubrir hasta 350m²dependiendo del mobiliario de la casa
-LIMPIEZA SIN ESFUERZO:diseño moderno, ligero, tan solo 1,1kg en tu mano, inteligente,con un sistema de rodillos ayudados por las ruedas, siendo necesario utilizar solo un 25 %del esfuerzo habitual
-SISTEMA DE AUTOLIMPIEZA:activa la función con tan solo pulsar un botón y, una vez lavado el rodillo, solo tienes que dejarlopreviamente secarpara que esté listo para la siguiente sesión de limpieza mientras se carga en la base</t>
+          <t>【Potente succión de 20000Pa】Esta aspiradora de mano ofrece una potencia de 20000 Pa, perfecta para aspirar polvo, migas y líquidos derramados sin esfuerzo. Su motor de alto rendimiento garantiza una limpieza profunda en cualquier superficie, ya sea en seco o sobre pequeños derrames.
+【Ligera, portátil y fácil de guardar】Con un peso de solo 400 gramos, esta aspiradora de mano es tan compacta que no ocupa espacio y cabe en cualquier rincón del hogar o del coche. Su diseño ergonómico permite usarla cómodamente con una sola mano, ideal para llevarla de viaje o para limpiezas rápidas. Las aspiradoras de mano como esta hacen que la limpieza diaria sea muy cómoda.
+【Carga rápida】Esta aspiradora de mano se carga rápidamente y te ofrece entre 20 y 30 minutos de uso continuo. Es perfecta para limpiezas exprés sin interrupciones. Tener siempre lista una aspiradora de mano en pocos minutos es la solución más práctica para mantener tu espacio impecable en todo momento.
+【Filtro lavable y reutilizable】El filtro de esta aspiradora de mano es totalmente lavable con agua, lo que permite un mantenimiento sencillo y conserva la máxima potencia de succión durante más tiempo. Las aspiradoras de mano con filtro lavable son más económicas, ya que no necesitas comprar recambios constantemente y reduces residuos.
+【Funcionamiento silencioso por debajo de 73dB】A pesar de su gran potencia, esta aspiradora de mano funciona con un nivel de ruido inferior a 73 dB, mucho más silenciosa que otros modelos. Puedes limpiar sin molestar a tu familia ni a tus mascotas.</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.es/dp/B0DGV9F4X3?psc=1</t>
+          <t>https://www.amazon.es/dp/B0H8ZM49W9?psc=1</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31mSTnwM6cL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41zcF9kihLL._AC_SR600,600_.jpg</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>B0DKMVFHRN</t>
+          <t>B0H8ZM49W9</t>
         </is>
       </c>
       <c r="M6" s="14" t="inlineStr">
@@ -2741,7 +2685,7 @@
         </is>
       </c>
       <c r="O6" s="15">
-        <v>223853</v>
+        <v>100170</v>
       </c>
       <c r="P6" s="15"/>
       <c r="Q6" s="16">
@@ -2754,7 +2698,7 @@
       </c>
       <c r="S6" s="18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T6" s="15"/>
@@ -2765,21 +2709,15 @@
       <c r="Y6" s="19">
         <v>1</v>
       </c>
-      <c r="Z6" s="20">
-        <v>371.88</v>
-      </c>
+      <c r="Z6" s="20"/>
       <c r="AA6" s="4"/>
       <c r="AB6" s="1"/>
       <c r="AC6" s="2"/>
-      <c r="AD6" s="19">
-        <v>783</v>
-      </c>
+      <c r="AD6" s="19"/>
       <c r="AE6" s="15">
-        <v>71</v>
-      </c>
-      <c r="AF6" s="21">
-        <v>4.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF6" s="21"/>
       <c r="AG6" s="22">
         <v>0</v>
       </c>
@@ -2788,17 +2726,11 @@
         <v>0</v>
       </c>
       <c r="AJ6"/>
-      <c r="AK6" s="13" t="inlineStr">
-        <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AL6" s="19">
-        <v>663</v>
-      </c>
+      <c r="AK6" s="13"/>
+      <c r="AL6" s="19"/>
       <c r="AM6" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN6" s="13"/>
@@ -2810,218 +2742,42 @@
       </c>
       <c r="AS6" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>shanximeixiandingshengganggougongchengyouxiangon</t>
         </is>
       </c>
       <c r="AT6" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU6" s="13"/>
       <c r="AV6" s="14"/>
-      <c r="AW6" s="13"/>
+      <c r="AW6" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1IIXB8MBW34P6</t>
+        </is>
+      </c>
       <c r="AX6" s="13"/>
       <c r="AY6" s="13"/>
       <c r="AZ6" s="13"/>
       <c r="BA6" s="13"/>
       <c r="BB6" s="13"/>
-      <c r="BC6" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD6" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC6" s="13"/>
+      <c r="BD6" s="13"/>
       <c r="BE6" s="13"/>
-      <c r="BF6" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF6" s="13"/>
       <c r="BG6" s="13"/>
       <c r="BH6" s="14"/>
       <c r="BI6"/>
-      <c r="BJ6" s="23" t="inlineStr">
-        <is>
-          <t>5,4 Kilogramos</t>
-        </is>
-      </c>
-      <c r="BK6" s="23" t="inlineStr">
-        <is>
-          <t>5.40 kg</t>
-        </is>
-      </c>
-      <c r="BL6" s="23" t="inlineStr">
-        <is>
-          <t>31,5l. x 30,5an. x 114,7al. centímetros</t>
-        </is>
-      </c>
+      <c r="BJ6" s="23"/>
+      <c r="BK6" s="23"/>
+      <c r="BL6" s="23"/>
       <c r="BM6" s="23"/>
       <c r="BN6" s="23"/>
       <c r="BO6" s="23"/>
       <c r="BP6" s="23"/>
       <c r="BQ6" s="23"/>
       <c r="BR6" s="13"/>
-    </row>
-    <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13">
-        <v>6</v>
-      </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>B0H8ZM49W9</t>
-        </is>
-      </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>KSIWEHDSS</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=KSIWEHDSS</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>Aspiradoras de Mano, Aspirador Coche Potente 20000Pa,Recargable Aspiradora De Mano Sin Cable,Mini Aspiradora para Hogar,Pelo de Mascotas</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>【Potente succión de 20000Pa】Esta aspiradora de mano ofrece una potencia de 20000 Pa, perfecta para aspirar polvo, migas y líquidos derramados sin esfuerzo. Su motor de alto rendimiento garantiza una limpieza profunda en cualquier superficie, ya sea en seco o sobre pequeños derrames.
-【Ligera, portátil y fácil de guardar】Con un peso de solo 400 gramos, esta aspiradora de mano es tan compacta que no ocupa espacio y cabe en cualquier rincón del hogar o del coche. Su diseño ergonómico permite usarla cómodamente con una sola mano, ideal para llevarla de viaje o para limpiezas rápidas. Las aspiradoras de mano como esta hacen que la limpieza diaria sea muy cómoda.
-【Carga rápida】Esta aspiradora de mano se carga rápidamente y te ofrece entre 20 y 30 minutos de uso continuo. Es perfecta para limpiezas exprés sin interrupciones. Tener siempre lista una aspiradora de mano en pocos minutos es la solución más práctica para mantener tu espacio impecable en todo momento.
-【Filtro lavable y reutilizable】El filtro de esta aspiradora de mano es totalmente lavable con agua, lo que permite un mantenimiento sencillo y conserva la máxima potencia de succión durante más tiempo. Las aspiradoras de mano con filtro lavable son más económicas, ya que no necesitas comprar recambios constantemente y reduces residuos.
-【Funcionamiento silencioso por debajo de 73dB】A pesar de su gran potencia, esta aspiradora de mano funciona con un nivel de ruido inferior a 73 dB, mucho más silenciosa que otros modelos. Puedes limpiar sin molestar a tu familia ni a tus mascotas.</t>
-        </is>
-      </c>
-      <c r="J7" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/dp/B0H8ZM49W9?psc=1</t>
-        </is>
-      </c>
-      <c r="K7" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41zcF9kihLL._AC_SR600,600_.jpg</t>
-        </is>
-      </c>
-      <c r="L7" s="14" t="inlineStr">
-        <is>
-          <t>B0H8ZM49W9</t>
-        </is>
-      </c>
-      <c r="M7" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina:Aspiración, limpieza y cuidado de suelo y ventanas:Aspiradoras:Aspiradoras domésticas para sólidos y líquidos</t>
-        </is>
-      </c>
-      <c r="N7" s="14" t="inlineStr">
-        <is>
-          <t>Hogar y cocina</t>
-        </is>
-      </c>
-      <c r="O7" s="15">
-        <v>100170</v>
-      </c>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="16">
-        <v>0</v>
-      </c>
-      <c r="R7" s="17" t="inlineStr">
-        <is>
-          <t>Aspiradoras domésticas para sólidos y líquidos</t>
-        </is>
-      </c>
-      <c r="S7" s="18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T7" s="15"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="15"/>
-      <c r="W7" s="15"/>
-      <c r="X7" s="15"/>
-      <c r="Y7" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="4"/>
-      <c r="AB7" s="1"/>
-      <c r="AC7" s="2"/>
-      <c r="AD7" s="19"/>
-      <c r="AE7" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="21"/>
-      <c r="AG7" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="20"/>
-      <c r="AI7" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ7"/>
-      <c r="AK7" s="13"/>
-      <c r="AL7" s="19"/>
-      <c r="AM7" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN7" s="13"/>
-      <c r="AO7" s="13"/>
-      <c r="AP7" s="20"/>
-      <c r="AQ7" s="19"/>
-      <c r="AR7" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS7" s="14" t="inlineStr">
-        <is>
-          <t>shanximeixiandingshengganggougongchengyouxiangon</t>
-        </is>
-      </c>
-      <c r="AT7" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU7" s="13"/>
-      <c r="AV7" s="14"/>
-      <c r="AW7" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1IIXB8MBW34P6</t>
-        </is>
-      </c>
-      <c r="AX7" s="13"/>
-      <c r="AY7" s="13"/>
-      <c r="AZ7" s="13"/>
-      <c r="BA7" s="13"/>
-      <c r="BB7" s="13"/>
-      <c r="BC7" s="13"/>
-      <c r="BD7" s="13"/>
-      <c r="BE7" s="13"/>
-      <c r="BF7" s="13"/>
-      <c r="BG7" s="13"/>
-      <c r="BH7" s="14"/>
-      <c r="BI7"/>
-      <c r="BJ7" s="23"/>
-      <c r="BK7" s="23"/>
-      <c r="BL7" s="23"/>
-      <c r="BM7" s="23"/>
-      <c r="BN7" s="23"/>
-      <c r="BO7" s="23"/>
-      <c r="BP7" s="23"/>
-      <c r="BQ7" s="23"/>
-      <c r="BR7" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3048,36 +2804,29 @@
     <hyperlink ref="L4" r:id="rId19" tooltip="https://www.amazon.es/dp/B0H63F8TQZ"/>
     <hyperlink ref="M4" r:id="rId20" tooltip="https://www.amazon.es/b?node=218878925031"/>
     <hyperlink ref="N4" r:id="rId21"/>
-    <hyperlink ref="C5" r:id="rId22" tooltip="https://www.amazon.es/dp/B0D2KT41N3"/>
-    <hyperlink ref="G5" r:id="rId23" tooltip="https://www.amazon.es/stores/Cecotec/page/8A5D1609-A164-427A-9580-48312AC42537?lp_asin=B0D2KT41N3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J5" r:id="rId24" tooltip="https://www.amazon.es/dp/B0D2KT41N3?psc=1"/>
-    <hyperlink ref="K5" r:id="rId25" tooltip="https://m.media-amazon.com/images/I/41k5oav-AKL._AC_US600_.jpg"/>
-    <hyperlink ref="L5" r:id="rId26" tooltip="https://www.amazon.es/dp/B0D33D9J3P"/>
+    <hyperlink ref="C5" r:id="rId22" tooltip="https://www.amazon.es/dp/B0DGV9F4X3"/>
+    <hyperlink ref="G5" r:id="rId23" tooltip="https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J5" r:id="rId24" tooltip="https://www.amazon.es/dp/B0DGV9F4X3?psc=1"/>
+    <hyperlink ref="K5" r:id="rId25" tooltip="https://m.media-amazon.com/images/I/31mSTnwM6cL._AC_US600_.jpg"/>
+    <hyperlink ref="L5" r:id="rId26" tooltip="https://www.amazon.es/dp/B0DKMVFHRN"/>
     <hyperlink ref="M5" r:id="rId27" tooltip="https://www.amazon.es/b?node=218878925031"/>
     <hyperlink ref="N5" r:id="rId28"/>
-    <hyperlink ref="C6" r:id="rId29" tooltip="https://www.amazon.es/dp/B0DGV9F4X3"/>
-    <hyperlink ref="G6" r:id="rId30" tooltip="https://www.amazon.es/stores/ROWENTA/page/3D429753-5927-4DBC-8D40-68488A481BD0?lp_asin=B0DGV9F4X3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J6" r:id="rId31" tooltip="https://www.amazon.es/dp/B0DGV9F4X3?psc=1"/>
-    <hyperlink ref="K6" r:id="rId32" tooltip="https://m.media-amazon.com/images/I/31mSTnwM6cL._AC_US600_.jpg"/>
-    <hyperlink ref="L6" r:id="rId33" tooltip="https://www.amazon.es/dp/B0DKMVFHRN"/>
+    <hyperlink ref="C6" r:id="rId29" tooltip="https://www.amazon.es/dp/B0H8ZM49W9"/>
+    <hyperlink ref="G6" r:id="rId30" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=KSIWEHDSS"/>
+    <hyperlink ref="J6" r:id="rId31" tooltip="https://www.amazon.es/dp/B0H8ZM49W9?psc=1"/>
+    <hyperlink ref="K6" r:id="rId32" tooltip="https://m.media-amazon.com/images/I/41zcF9kihLL._AC_SR600,600_.jpg"/>
+    <hyperlink ref="L6" r:id="rId33" tooltip="https://www.amazon.es/dp/B0H8ZM49W9"/>
     <hyperlink ref="M6" r:id="rId34" tooltip="https://www.amazon.es/b?node=218878925031"/>
     <hyperlink ref="N6" r:id="rId35"/>
-    <hyperlink ref="C7" r:id="rId36" tooltip="https://www.amazon.es/dp/B0H8ZM49W9"/>
-    <hyperlink ref="G7" r:id="rId37" tooltip="https://www.amazon.es/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=KSIWEHDSS"/>
-    <hyperlink ref="J7" r:id="rId38" tooltip="https://www.amazon.es/dp/B0H8ZM49W9?psc=1"/>
-    <hyperlink ref="K7" r:id="rId39" tooltip="https://m.media-amazon.com/images/I/41zcF9kihLL._AC_SR600,600_.jpg"/>
-    <hyperlink ref="L7" r:id="rId40" tooltip="https://www.amazon.es/dp/B0H8ZM49W9"/>
-    <hyperlink ref="M7" r:id="rId41" tooltip="https://www.amazon.es/b?node=218878925031"/>
-    <hyperlink ref="N7" r:id="rId42"/>
-    <hyperlink ref="AW7" r:id="rId43" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1IIXB8MBW34P6"/>
+    <hyperlink ref="AW6" r:id="rId36" tooltip="https://www.amazon.es/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1IIXB8MBW34P6"/>
   </hyperlinks>
-  <drawing r:id="rId44"/>
+  <drawing r:id="rId37"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -3141,7 +2890,7 @@
         <v>339.0</v>
       </c>
       <c r="G2" s="22">
-        <v>0.5208333333333334</v>
+        <v>0.7191201353637902</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3162,46 +2911,25 @@
         <v>288.06024096385545</v>
       </c>
       <c r="G3" s="22">
-        <v>0.2034313725490196</v>
+        <v>0.2808798646362098</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>KSIWEHDSS</t>
         </is>
       </c>
       <c r="B4" s="15">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="C4" s="15">
-        <v>7421</v>
+        <v>0</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
-      <c r="F4" s="20">
-        <v>32.98222222222222</v>
-      </c>
+      <c r="F4" s="20"/>
       <c r="G4" s="22">
-        <v>0.2757352941176471</v>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>KSIWEHDSS</t>
-        </is>
-      </c>
-      <c r="B5" s="15">
-        <v>0</v>
-      </c>
-      <c r="C5" s="15">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="22">
         <v>0.0</v>
       </c>
     </row>
@@ -3266,15 +2994,15 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>816</v>
+        <v>591</v>
       </c>
       <c r="C2" s="15">
-        <v>199314</v>
+        <v>191893</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>244.25735294117646</v>
+        <v>324.69204737732656</v>
       </c>
       <c r="G2" s="22">
         <v>1.0</v>
